--- a/bemenet_eredmenyek.xlsx
+++ b/bemenet_eredmenyek.xlsx
@@ -58,7 +58,7 @@
     <x:t>Balatonfüred</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
+    <x:t>120</x:t>
   </x:si>
   <x:si>
     <x:t>Ady Endre utca 14/2</x:t>
@@ -70,9 +70,6 @@
     <x:t>Balatonfüred, Széchenyi utca 2</x:t>
   </x:si>
   <x:si>
-    <x:t>120</x:t>
-  </x:si>
-  <x:si>
     <x:t>Megnyitás</x:t>
   </x:si>
   <x:si>
@@ -88,37 +85,16 @@
     <x:t>13</x:t>
   </x:si>
   <x:si>
-    <x:t>Ady Endre utca 18/B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Balatonfüred, Honvéd utca 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>130</x:t>
-  </x:si>
-  <x:si>
-    <x:t>562043,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>179623,0</x:t>
+    <x:t>✗ Hiba</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRSZ nem található pontosan: 13</x:t>
   </x:si>
   <x:si>
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>Ady Endre utca 42/A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Balatonfüred, Jókai Mór utca 26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>140</x:t>
-  </x:si>
-  <x:si>
-    <x:t>561969,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>179721,5</x:t>
+    <x:t>HRSZ nem található pontosan: 14</x:t>
   </x:si>
   <x:si>
     <x:t>Alsó köz 2/A</x:t>
@@ -127,16 +103,25 @@
     <x:t>Cím</x:t>
   </x:si>
   <x:si>
-    <x:t>✗ Hiba</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nem található találat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alsó Muskátli utca 2/A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alsó Muskátli utca 6/A</x:t>
+    <x:t>Cím nem található pontosan: Alsó köz 2/A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gödöllő</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Szarvas utca 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gödöllő, Szarvas utca 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3942/6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>674377,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252038,2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -185,12 +170,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF0F8FF"/>
+        <x:fgColor rgb="FFF08080"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF08080"/>
+        <x:fgColor rgb="FFF0F8FF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -213,7 +198,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="7">
+  <x:cellStyleXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -226,9 +211,6 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -236,7 +218,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -250,10 +232,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -560,21 +538,21 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:M7"/>
+  <x:dimension ref="A1:M6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="15.282054" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18.996339" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="12.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="29.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28.567768" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.710625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.567768" style="0" customWidth="1"/>
     <x:col min="8" max="9" width="8.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.567768" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="8.710625" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="12.567768" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="19.567768" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="38.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:13">
@@ -635,19 +613,19 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G2" s="2" t="s">
+      <x:c r="H2" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
+      <x:c r="I2" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="K2" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
         <x:v>11</x:v>
@@ -658,167 +636,117 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
       <x:c r="J3" s="3"/>
       <x:c r="K3" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L3" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M3" s="3" t="s"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L3" s="3"/>
+      <x:c r="M3" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:13">
       <x:c r="A4" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s"/>
       <x:c r="D4" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H4" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I4" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
       <x:c r="J4" s="3"/>
       <x:c r="K4" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L4" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M4" s="3" t="s"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L4" s="3"/>
+      <x:c r="M4" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" spans="1:13">
-      <x:c r="A5" s="5" t="s">
+      <x:c r="A5" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="s"/>
-      <x:c r="C5" s="5" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="s"/>
-      <x:c r="F5" s="5" t="s"/>
-      <x:c r="G5" s="6" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H5" s="5" t="s"/>
-      <x:c r="I5" s="5" t="s"/>
-      <x:c r="J5" s="5"/>
-      <x:c r="K5" s="5" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="L5" s="5"/>
-      <x:c r="M5" s="5" t="s">
-        <x:v>38</x:v>
+      <x:c r="B5" s="3" t="s"/>
+      <x:c r="C5" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s"/>
+      <x:c r="F5" s="3" t="s"/>
+      <x:c r="G5" s="3"/>
+      <x:c r="H5" s="3" t="s"/>
+      <x:c r="I5" s="3" t="s"/>
+      <x:c r="J5" s="3"/>
+      <x:c r="K5" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L5" s="3"/>
+      <x:c r="M5" s="3" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:13">
-      <x:c r="A6" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s"/>
-      <x:c r="C6" s="5" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E6" s="5" t="s"/>
-      <x:c r="F6" s="5" t="s"/>
-      <x:c r="G6" s="6" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H6" s="5" t="s"/>
-      <x:c r="I6" s="5" t="s"/>
-      <x:c r="J6" s="5"/>
-      <x:c r="K6" s="5" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="L6" s="5"/>
-      <x:c r="M6" s="5" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:13">
-      <x:c r="A7" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s"/>
-      <x:c r="C7" s="5" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E7" s="5" t="s"/>
-      <x:c r="F7" s="5" t="s"/>
-      <x:c r="G7" s="6" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H7" s="5" t="s"/>
-      <x:c r="I7" s="5" t="s"/>
-      <x:c r="J7" s="5"/>
-      <x:c r="K7" s="5" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="L7" s="5"/>
-      <x:c r="M7" s="5" t="s">
-        <x:v>38</x:v>
-      </x:c>
+      <x:c r="A6" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s"/>
+      <x:c r="C6" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G6" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H6" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I6" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J6" s="4"/>
+      <x:c r="K6" s="4" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L6" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M6" s="4" t="s"/>
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
     <x:hyperlink ref="G2" r:id="rId5"/>
     <x:hyperlink ref="L2" r:id="rId6"/>
-    <x:hyperlink ref="G3" r:id="rId7"/>
-    <x:hyperlink ref="L3" r:id="rId8"/>
-    <x:hyperlink ref="G4" r:id="rId9"/>
-    <x:hyperlink ref="L4" r:id="rId10"/>
-    <x:hyperlink ref="G5" r:id="rId11"/>
-    <x:hyperlink ref="G6" r:id="rId12"/>
-    <x:hyperlink ref="G7" r:id="rId13"/>
+    <x:hyperlink ref="G6" r:id="rId7"/>
+    <x:hyperlink ref="L6" r:id="rId8"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bemenet_eredmenyek.xlsx
+++ b/bemenet_eredmenyek.xlsx
@@ -55,6 +55,21 @@
     <x:t>Hiba</x:t>
   </x:si>
   <x:si>
+    <x:t>Varos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRSZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CÍM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>✗ Hiba</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Település nem található pontosan: Varos</x:t>
+  </x:si>
+  <x:si>
     <x:t>Balatonfüred</x:t>
   </x:si>
   <x:si>
@@ -64,9 +79,6 @@
     <x:t>Ady Endre utca 14/2</x:t>
   </x:si>
   <x:si>
-    <x:t>HRSZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>Balatonfüred, Széchenyi utca 2</x:t>
   </x:si>
   <x:si>
@@ -85,9 +97,6 @@
     <x:t>13</x:t>
   </x:si>
   <x:si>
-    <x:t>✗ Hiba</x:t>
-  </x:si>
-  <x:si>
     <x:t>HRSZ nem található pontosan: 13</x:t>
   </x:si>
   <x:si>
@@ -122,6 +131,45 @@
   </x:si>
   <x:si>
     <x:t>252038,2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252038,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3942/8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gödöllő, Szarvas utca 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>674400,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252058,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mókus utca 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cím nem található pontosan: Mókus utca 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dunakeszi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Madách Imre utca 11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dunakeszi, Madách Imre utca 11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>656894,4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>255807,8</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -198,14 +246,11 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -218,16 +263,12 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -538,21 +579,21 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:M6"/>
+  <x:dimension ref="A1:M11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="15.282054" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18.996339" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="12.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30.139196" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.710625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.567768" style="0" customWidth="1"/>
     <x:col min="8" max="9" width="8.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.567768" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="8.710625" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="12.567768" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="38.710625" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="39.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:13">
@@ -597,156 +638,323 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:13">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s"/>
+      <x:c r="F2" s="2" t="s"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2" t="s"/>
+      <x:c r="I2" s="2" t="s"/>
+      <x:c r="J2" s="2"/>
+      <x:c r="K2" s="2" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="L2" s="2"/>
+      <x:c r="M2" s="2" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L2" s="2" t="s">
-        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:13">
       <x:c r="A3" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="J3" s="3"/>
       <x:c r="K3" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L3" s="3"/>
-      <x:c r="M3" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L3" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:13">
-      <x:c r="A4" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
+      <x:c r="A4" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s"/>
+      <x:c r="D4" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="s"/>
+      <x:c r="F4" s="2" t="s"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2" t="s"/>
+      <x:c r="I4" s="2" t="s"/>
+      <x:c r="J4" s="2"/>
+      <x:c r="K4" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L4" s="2"/>
+      <x:c r="M4" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:13">
+      <x:c r="A5" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s"/>
+      <x:c r="D5" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="s"/>
+      <x:c r="F5" s="2" t="s"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2" t="s"/>
+      <x:c r="I5" s="2" t="s"/>
+      <x:c r="J5" s="2"/>
+      <x:c r="K5" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L5" s="2"/>
+      <x:c r="M5" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:13">
+      <x:c r="A6" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s"/>
+      <x:c r="C6" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E6" s="2" t="s"/>
+      <x:c r="F6" s="2" t="s"/>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="2" t="s"/>
+      <x:c r="I6" s="2" t="s"/>
+      <x:c r="J6" s="2"/>
+      <x:c r="K6" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L6" s="2"/>
+      <x:c r="M6" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:13">
+      <x:c r="A7" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s"/>
+      <x:c r="C7" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H7" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I7" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s">
+      <x:c r="L7" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="3" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:13">
+      <x:c r="A8" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s"/>
+      <x:c r="D8" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G8" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H8" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I8" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L8" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M8" s="3" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:13">
+      <x:c r="A9" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="s"/>
+      <x:c r="D9" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I9" s="3" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J9" s="3"/>
+      <x:c r="K9" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M9" s="3" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:13">
+      <x:c r="A10" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="s"/>
+      <x:c r="C10" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="s"/>
+      <x:c r="F10" s="2" t="s"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2" t="s"/>
+      <x:c r="I10" s="2" t="s"/>
+      <x:c r="J10" s="2"/>
+      <x:c r="K10" s="2" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3"/>
-      <x:c r="K4" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L4" s="3"/>
-      <x:c r="M4" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:13">
-      <x:c r="A5" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s"/>
-      <x:c r="C5" s="3" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="s"/>
-      <x:c r="F5" s="3" t="s"/>
-      <x:c r="G5" s="3"/>
-      <x:c r="H5" s="3" t="s"/>
-      <x:c r="I5" s="3" t="s"/>
-      <x:c r="J5" s="3"/>
-      <x:c r="K5" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L5" s="3"/>
-      <x:c r="M5" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:13">
-      <x:c r="A6" s="4" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="s"/>
-      <x:c r="C6" s="4" t="s">
+      <x:c r="L10" s="2"/>
+      <x:c r="M10" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:13">
+      <x:c r="A11" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="s"/>
+      <x:c r="C11" s="3" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F6" s="4" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G6" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="4" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I6" s="4" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="J6" s="4"/>
-      <x:c r="K6" s="4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L6" s="5" t="s">
+      <x:c r="E11" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G11" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H11" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I11" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J11" s="3">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K11" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L11" s="4" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M6" s="4" t="s"/>
+      <x:c r="M11" s="3" t="s"/>
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="G2" r:id="rId5"/>
-    <x:hyperlink ref="L2" r:id="rId6"/>
-    <x:hyperlink ref="G6" r:id="rId7"/>
-    <x:hyperlink ref="L6" r:id="rId8"/>
+    <x:hyperlink ref="G3" r:id="rId5"/>
+    <x:hyperlink ref="L3" r:id="rId6"/>
+    <x:hyperlink ref="G7" r:id="rId7"/>
+    <x:hyperlink ref="L7" r:id="rId8"/>
+    <x:hyperlink ref="G8" r:id="rId9"/>
+    <x:hyperlink ref="L8" r:id="rId10"/>
+    <x:hyperlink ref="G9" r:id="rId11"/>
+    <x:hyperlink ref="L9" r:id="rId12"/>
+    <x:hyperlink ref="G11" r:id="rId13"/>
+    <x:hyperlink ref="L11" r:id="rId14"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
